--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_nearest_dose_acrt.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_nearest_dose_acrt.xlsx
@@ -488,10 +488,10 @@
         <v>-19199.0160708592</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>27292.7902395755</v>
+        <v>25218.125142705</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>-18784.8006431627</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>26734.918161052</v>
+        <v>24626.2738068772</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>-18518.6219859513</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>26368.6661584401</v>
+        <v>24246.1975254967</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>-16812.6295511348</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>23594.9713228182</v>
+        <v>21757.3823757789</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>-16337.9913509696</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>22826.1363929128</v>
+        <v>21063.9902336064</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>-15689.2825403337</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>21777.5201446061</v>
+        <v>20052.893300086</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>-14992.6448978684</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>20654.3998450857</v>
+        <v>19102.1978334688</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>-14556.8132515523</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>19953.4075466107</v>
+        <v>18467.8922093802</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>-14556.8132515523</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>19953.4075466107</v>
+        <v>18467.8922093802</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>-14169.3016955983</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>19331.2589752748</v>
+        <v>17904.4522020334</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>-13427.5701724561</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>18143.5300154824</v>
+        <v>16784.686621182</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>-13217.8755677005</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>17808.5265226956</v>
+        <v>16463.915927551</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>-12565.0212681403</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>16767.8724740369</v>
+        <v>15454.5278186272</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>-12202.8025989514</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>16192.0887425343</v>
+        <v>14969.3604014092</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>-11475.5301023656</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>15039.6978380355</v>
+        <v>14094.3418008221</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>-11304.620499159</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>14769.6365536597</v>
+        <v>13868.2168153844</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>-11121.5370857246</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>14480.6709860442</v>
+        <v>13637.4440459005</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>-9442.43791543739</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>12029.6362408299</v>
+        <v>11224.0267368597</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>-8492.58614281015</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>10673.9345913096</v>
+        <v>9970.51508910658</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>-8492.58614281015</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>10673.9345913096</v>
+        <v>9970.51508910658</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>-7926.18986793621</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>9869.78239589679</v>
+        <v>9347.5858744991</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>-7235.88337135084</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>8894.59271044043</v>
+        <v>8430.55848721199</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>-7069.09840042475</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>8659.8572621339</v>
+        <v>8250.10239351582</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>-6221.31152020773</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>7472.61731759401</v>
+        <v>6853.10278409666</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>-5850.01025216316</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>6956.11103453112</v>
+        <v>6539.03243673896</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>-5615.46189555367</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>6631.05311687536</v>
+        <v>6256.21058023497</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>-4080.02914845657</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>4531.32634880444</v>
+        <v>3968.51404800107</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>-3510.12547260682</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>3767.76643507223</v>
+        <v>3348.81607496426</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>-3320.27199993933</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>3515.84777488555</v>
+        <v>3120.19548922525</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>-3128.11259416271</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>3262.28027407174</v>
+        <v>2851.11957652266</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>-2881.3244117841</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>2938.90548048479</v>
+        <v>2707.71978341397</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>-2394.60510784274</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>2309.83709354738</v>
+        <v>2149.53345946452</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>-1446.86802347425</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>1130.7260635154</v>
+        <v>1837.36087265512</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>-1242.71803728184</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>892.253771871682</v>
+        <v>1653.47710720333</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>-1065.79930063313</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>888.786346822004</v>
+        <v>1634.84641651491</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>-819.074321495687</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>879.054702961383</v>
+        <v>1719.02759097875</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>-687.768817315819</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>870.959820707204</v>
+        <v>1602.85265482936</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>-512.63778535632</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>856.055963645355</v>
+        <v>1690.62621661574</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>-485.927302056353</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>853.287666782592</v>
+        <v>1696.64819146194</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>75.4893945677683</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>594.242402820346</v>
+        <v>1948.96681056489</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>234.009002733331</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>457.925364952155</v>
+        <v>1841.07005053615</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>255.451481922028</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>428.587069064016</v>
+        <v>1812.60427286751</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>308.907702710002</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>355.584396173571</v>
+        <v>1773.03665711195</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>336.229373568497</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>322.362784549121</v>
+        <v>1732.19512140297</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>380.620964849794</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>286.250854228764</v>
+        <v>1645.64263740438</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>592.951305508395</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>144.787141687514</v>
+        <v>1338.7690921627</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>714.598139747968</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>211.912183355433</v>
+        <v>1261.38981499645</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>891.978749859591</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>310.393012179142</v>
+        <v>989.811694238925</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>1036.1420798974</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>391.077493830875</v>
+        <v>804.426312816176</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>1107.66629148759</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>431.371002947149</v>
+        <v>733.22010607275</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>1146.8972148804</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>388.619764079904</v>
+        <v>652.861117035925</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>1146.8972148804</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>388.619764079904</v>
+        <v>652.861117035925</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>1165.87903470487</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>380.329721531472</v>
+        <v>626.259055907323</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>1208.50638603105</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>426.891377551554</v>
+        <v>595.546340105151</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>1265.78433821501</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>489.469142493442</v>
+        <v>634.305454151074</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>1286.95050059063</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>512.597998548306</v>
+        <v>647.624018106319</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>1408.7242161294</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>725.408819593756</v>
+        <v>742.482183970527</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>1447.13864803655</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>826.6822211085</v>
+        <v>711.749185751807</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>1516.06131090299</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>1012.35167663845</v>
+        <v>710.405961544502</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>1542.82382757675</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>1086.05608372451</v>
+        <v>757.158487183628</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>1691.96966692315</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>1383.00564337787</v>
+        <v>990.287239347023</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>1761.59040491733</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>1445.64037363962</v>
+        <v>1035.16007301692</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>1786.42311555252</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>1465.12663088688</v>
+        <v>1059.7734076597</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>1843.04003734245</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>1499.16146178852</v>
+        <v>1164.82859461796</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>1864.57343788798</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>1504.88819358482</v>
+        <v>1209.71161331934</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>1881.76374512446</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>1502.54088731885</v>
+        <v>1198.40742539294</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>1891.22104443185</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>1495.15059544228</v>
+        <v>1218.84461469401</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>1898.48582281058</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>1480.17275812035</v>
+        <v>1230.08035015176</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>1897.75915466419</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>1411.18484067519</v>
+        <v>1206.63354362162</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>1890.52042525071</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>1374.7237978078</v>
+        <v>1265.98019005309</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>1886.94215227264</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>1359.91937343814</v>
+        <v>1286.79001334775</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>1882.5513271599</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>1343.16634141878</v>
+        <v>1293.63521915161</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>1871.53606658506</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>1305.25326259715</v>
+        <v>1297.91952363016</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>1844.91405019504</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>1225.60123283598</v>
+        <v>1297.874637338</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>1805.43653219193</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>1121.26944169783</v>
+        <v>1362.75693240679</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>1725.06911849654</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>929.928991715654</v>
+        <v>1303.92222973738</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>1707.96731721791</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>891.250442004087</v>
+        <v>1287.73175602991</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>1600.51212887444</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>842.328987122553</v>
+        <v>1293.38263997185</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>1487.02181869814</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>745.040407608546</v>
+        <v>1275.55535715511</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>1428.61414135905</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>682.074682165657</v>
+        <v>1256.66287040665</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>1280.00303490984</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>699.912776257958</v>
+        <v>1277.78185620774</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>1270.83297279993</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>705.234504005122</v>
+        <v>1282.09592704832</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>1099.48760899316</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>630.995289908956</v>
+        <v>1177.65909705633</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>902.112106541861</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>544.033661652857</v>
+        <v>1277.10102044718</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>720.524167795339</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>545.709890577678</v>
+        <v>1308.74071916118</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>607.657277778205</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>617.013814793683</v>
+        <v>1280.11603500615</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>604.359668886412</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>619.093572302715</v>
+        <v>1280.7670052451</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>181.847286978509</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>884.204578632537</v>
+        <v>1367.31134085819</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>-534.537331358789</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>358.968498981012</v>
+        <v>2078.77549444169</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>-3073.02354605901</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>3266.73428896337</v>
+        <v>5309.13732791863</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>12.1123606027272</v>
+        <v>2.60257855843226</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
